--- a/results/reliability_eval/reliability_eval_09-17-1-test/Llama-3-8B_P101_0_sample_25_tokens_0.1_temp_reflective_reasoning_raw_table_09-17-1-test.xlsx
+++ b/results/reliability_eval/reliability_eval_09-17-1-test/Llama-3-8B_P101_0_sample_25_tokens_0.1_temp_reflective_reasoning_raw_table_09-17-1-test.xlsx
@@ -510,7 +510,7 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>://www.wikipedia.org/wiki/Alan_Turing
-://www.wikipedia.org/wiki/Alan_Turing</t>
+://en.wikipedia.org/wiki/Alan_Turing</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -530,7 +530,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Alan', 1.0), ('_T', 1.0), ('uring', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Alan', 1.0), ('_T', 1.0), ('uring', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Alan', 1.0), ('_T', 1.0), ('uring', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Alan', 1.0), ('_T', 1.0), ('uring', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -933,27 +933,27 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>://www.wikipedia.org/wiki/Anaxagoras
-://www.wikipedia.org/wiki/Anaxagoras</t>
+://en.wikipedia.org/wiki/Anaxagoras</t>
         </is>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9829981923103333</v>
+        <v>0.9587278366088867</v>
       </c>
       <c r="I11" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0)]</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -980,27 +980,27 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>://www.wikipedia.org/wiki/Anaxagoras
-://www.wikipedia.org/wiki/Anaxagoras</t>
+://en.wikipedia.org/wiki/Anaxagoras</t>
         </is>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9829981923103333</v>
+        <v>0.9587278366088867</v>
       </c>
       <c r="I12" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.6514), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.3486), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('An', 1.0), ('ax', 1.0), ('ag', 1.0), ('oras', 1.0)]</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1446,28 +1446,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>://www.wikipedia.org/wiki/Al_Capp
-://www.wikipedia.org/wiki/Al_Capp</t>
+          <t>://www.google.com/url?q=https://www.google.com/url?q=https://www.google.com/url?q=https://www</t>
         </is>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6513549089431763</v>
+        <v>0.3486451208591461</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9829981923103333</v>
+        <v>0.9587278366088867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.279236227273941</v>
+        <v>0.3673676252365112</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 0.6514), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Al', 1.0), ('_C', 1.0), ('app', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/', 1.0), ('Al', 1.0), ('_C', 1.0), ('app', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 0.3486), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('www', 1.0), ('.google', 1.0), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('www', 1.0)]</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1493,27 +1492,28 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>://www.google.com/url?q=https://en.wikipedia.org/wiki/Benjamin_Lee_Whorf&amp;sa=D</t>
+          <t>://en.wikipedia.org/wiki/Benjamin_Lee_Whorf
+://en.wikipedia.org/wiki/Ben</t>
         </is>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9460576772689819</v>
+        <v>0.9726549386978149</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6931471824645996</v>
+        <v>0.3465735912322998</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 0.5), ('.google', 0.5), ('.com', 1.0), ('/url', 1.0), ('?q', 1.0), ('=https', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/B', 1.0), ('en', 1.0), ('jamin', 1.0), ('_L', 1.0), ('ee', 1.0), ('_', 1.0), ('Wh', 1.0), ('orf', 1.0), ('&amp;', 1.0), ('sa', 1.0), ('=D', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 0.5), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/B', 1.0), ('en', 1.0), ('jamin', 1.0), ('_L', 1.0), ('ee', 1.0), ('_', 1.0), ('Wh', 1.0), ('orf', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('en', 1.0), ('.wikipedia', 1.0), ('.org', 1.0), ('/wiki', 1.0), ('/B', 1.0), ('en', 1.0)]</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -1774,7 +1774,8 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>://www.bruceperens.com/://www.bruceperens.com/://</t>
+          <t>://www.bruceperens.com/bruceperens.html
+://www.bruceper</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1794,7 +1795,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0), ('ens', 1.0), ('.com', 1.0), ('/', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0), ('ens', 1.0), ('.com', 1.0), ('/', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0), ('ens', 1.0), ('.com', 1.0), ('/', 1.0), ('br', 0.5), ('uce', 1.0), ('per', 1.0), ('ens', 1.0), ('.html', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0)]</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -1866,7 +1867,8 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>://www.bruceperens.com/://www.bruceperens.com/://</t>
+          <t>://www.bruceperens.com/bruceperens.html
+://www.bruceper</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1886,7 +1888,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0), ('ens', 1.0), ('.com', 1.0), ('/', 1.0), ('&lt;|end_of_text|&gt;', 0.5), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0), ('ens', 1.0), ('.com', 1.0), ('/', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0)]</t>
+          <t>[('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0), ('ens', 1.0), ('.com', 1.0), ('/', 1.0), ('br', 0.5), ('uce', 1.0), ('per', 1.0), ('ens', 1.0), ('.html', 1.0), ('\n', 1.0), ('&lt;|end_of_text|&gt;', 1.0), ('&lt;|begin_of_text|&gt;', 1.0), ('://', 1.0), ('www', 1.0), ('.b', 1.0), ('ru', 1.0), ('ce', 1.0), ('per', 1.0)]</t>
         </is>
       </c>
       <c r="L31" t="n">
